--- a/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>10235</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.37897</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.81395999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>257</v>
-      </c>
-      <c r="J2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.37897</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.81396</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>10236</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.37896</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.81432</v>
-      </c>
-      <c r="I3" t="n">
-        <v>721</v>
-      </c>
-      <c r="J3" t="n">
-        <v>34</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.37896</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.81432</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>10237</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.378421</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.817818</v>
-      </c>
-      <c r="I4" t="n">
-        <v>381</v>
-      </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.378421</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.817818</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>FE Y ALEGRIA 69</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.37278</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.80777</v>
-      </c>
-      <c r="I5" t="n">
-        <v>770</v>
-      </c>
-      <c r="J5" t="n">
-        <v>49</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.37278</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.80777</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.378926</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.81645</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1262</v>
-      </c>
-      <c r="J6" t="n">
-        <v>75</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.378926</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.81645</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>TOMAS P. GALVEZ QUISPE</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.28146</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.960915</v>
-      </c>
-      <c r="I7" t="n">
-        <v>318</v>
-      </c>
-      <c r="J7" t="n">
-        <v>31</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.28146</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.960915</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>TORIBIO CASANOVA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.380292</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.815336</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1325</v>
-      </c>
-      <c r="J8" t="n">
-        <v>77</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.380292</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.815336</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>10748</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.141829</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.012404</v>
-      </c>
-      <c r="I9" t="n">
-        <v>20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.141829</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.012404</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.237078</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.71266300000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>227</v>
-      </c>
-      <c r="J10" t="n">
-        <v>24</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.237078</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.712663</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>16378</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.153439</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.685328</v>
-      </c>
-      <c r="I11" t="n">
-        <v>263</v>
-      </c>
-      <c r="J11" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.153439</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.685328</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>996</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.14186</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.01233000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.14186</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.01233</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>10234</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.382108</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.819322</v>
-      </c>
-      <c r="I13" t="n">
-        <v>450</v>
-      </c>
-      <c r="J13" t="n">
-        <v>24</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.382108</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.819322</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,22 +1253,280 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.38071</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.81917</v>
-      </c>
-      <c r="I14" t="n">
-        <v>456</v>
-      </c>
-      <c r="J14" t="n">
-        <v>35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.38071</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.81917</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>060601</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>111951</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.378534</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.816547</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>060601</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>349057</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.383651</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.819607</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>060601</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>597702</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PREMIUM COLLEGE FOR EXCELLENCE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-6.38284</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.815787</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>060601</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CUTERVO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>863480</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-6.38183</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.81976</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>112413</t>
+          <t>772611</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>996</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.37897</t>
+          <t>-6.14186</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.81396</t>
+          <t>-79.01233</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>112427</t>
+          <t>112413</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.37896</t>
+          <t>-6.37897</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.81432</t>
+          <t>-78.81396</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>112432</t>
+          <t>116939</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.378421</t>
+          <t>-6.153439</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.817818</t>
+          <t>-78.685328</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>263</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>115529</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 69</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.37278</t>
+          <t>-6.141829</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.80777</t>
+          <t>-79.012404</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>113276</t>
+          <t>112432</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.378926</t>
+          <t>-6.378421</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.81645</t>
+          <t>-78.817818</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>381</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>113375</t>
+          <t>116029</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TOMAS P. GALVEZ QUISPE</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.28146</t>
+          <t>-6.237078</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.960915</t>
+          <t>-78.712663</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>113380</t>
+          <t>863499</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TORIBIO CASANOVA</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.380292</t>
+          <t>-6.382108</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.815336</t>
+          <t>-78.819322</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>115529</t>
+          <t>113375</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>TOMAS P. GALVEZ QUISPE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.141829</t>
+          <t>-6.28146</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.012404</t>
+          <t>-78.960915</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>318</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>112427</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.237078</t>
+          <t>-6.37896</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.712663</t>
+          <t>-78.81432</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>721</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>116939</t>
+          <t>863507</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.153439</t>
+          <t>-6.38071</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.685328</t>
+          <t>-78.81917</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>456</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,37 +1121,37 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>772611</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>FE Y ALEGRIA 69</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.14186</t>
+          <t>-6.37278</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.01233</t>
+          <t>-78.80777</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>770</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>863499</t>
+          <t>113276</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.382108</t>
+          <t>-6.378926</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.819322</t>
+          <t>-78.81645</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>863507</t>
+          <t>113380</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>TORIBIO CASANOVA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.38071</t>
+          <t>-6.380292</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.81917</t>
+          <t>-78.815336</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>772611</t>
+          <t>863507</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.14186</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.01233</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-6.38071</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>-78.81917</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>112413</t>
+          <t>863499</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.37897</t>
+          <t>450</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.81396</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-6.382108</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.819322</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>116939</t>
+          <t>863480</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16378</t>
+          <t>328</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.153439</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.685328</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>-6.38183</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.81976</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>115529</t>
+          <t>772611</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>996</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.141829</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.012404</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-6.14186</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-79.01233</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>112432</t>
+          <t>597702</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10237</t>
+          <t>PREMIUM COLLEGE FOR EXCELLENCE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.378421</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.817818</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>-6.38284</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.815787</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>116029</t>
+          <t>349057</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JOSE CARLOS MARIATEGUI</t>
+          <t>567</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.237078</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.712663</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-6.383651</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.819607</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>863499</t>
+          <t>116939</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.382108</t>
+          <t>263</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.819322</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>-6.153439</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-78.685328</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>113375</t>
+          <t>116029</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TOMAS P. GALVEZ QUISPE</t>
+          <t>JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.28146</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.960915</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>-6.237078</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.712663</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,37 +997,37 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>112427</t>
+          <t>115529</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10236</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.37896</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.81432</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>-6.141829</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.012404</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>863507</t>
+          <t>113380</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>TORIBIO CASANOVA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.38071</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.81917</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>-6.380292</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-78.815336</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>113375</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 69</t>
+          <t>TOMAS P. GALVEZ QUISPE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.37278</t>
+          <t>318</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.80777</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>-6.28146</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-78.960915</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>-6.378926</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>-78.81645</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1262</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>113380</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TORIBIO CASANOVA</t>
+          <t>FE Y ALEGRIA 69</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.380292</t>
+          <t>770</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.815336</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>-6.37278</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>-78.80777</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>111951</t>
+          <t>112432</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.378534</t>
+          <t>381</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.816547</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>-6.378421</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.817818</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>349057</t>
+          <t>112427</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.383651</t>
+          <t>721</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.819607</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-6.37896</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-78.81432</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>597702</t>
+          <t>112413</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PREMIUM COLLEGE FOR EXCELLENCE</t>
+          <t>10235</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.38284</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.815787</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>-6.37897</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.81396</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>863480</t>
+          <t>111951</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>301</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.38183</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.81976</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>-6.378534</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.816547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">

--- a/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
+++ b/ZonasEscolares/excels/CAJAMARCA-CUTERVO-CUTERVO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
